--- a/catatan grok.xlsx
+++ b/catatan grok.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ERP\Miroservices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BD88D5B-3B6B-469B-857A-2FE1AA49264D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AA68DA-3802-4A46-8C8F-AF0446657770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{249B4D2E-D604-43D3-A713-D57BA1C3D09C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{249B4D2E-D604-43D3-A713-D57BA1C3D09C}"/>
   </bookViews>
   <sheets>
     <sheet name="role menu" sheetId="1" r:id="rId1"/>
+    <sheet name="security" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,6 +27,14 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>pilih opsi 1</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -258,6 +268,148 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>480524</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>45930</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18936A37-C871-4DA4-8DC0-04163BF440D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="182880"/>
+          <a:ext cx="5357324" cy="2423370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>130027</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>122390</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7E49747-3B88-4E34-98B5-9B80BCFB58A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="182880"/>
+          <a:ext cx="5616427" cy="5425910"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>53820</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>15558</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{626E0DD6-1097-4BDF-B7F4-D022D13B33B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="6217920"/>
+          <a:ext cx="5540220" cy="3673158"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -561,4 +713,30 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300579FB-C25B-4149-89D3-613E798F0371}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C01456A-799B-4381-ABAC-5BCE5D0A7543}">
+  <dimension ref="B33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>